--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260604.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260604.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>12.21%</t>
+          <t>12.26%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>11.17%</t>
+          <t>10.91%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>9.30%</t>
+          <t>9.23%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.30%</t>
+          <t>7.33%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.39%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.49%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.58%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.56%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -1034,24 +1034,24 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>GNRC US</t>
+          <t>PEG US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>基內瑞克控股公司</t>
+          <t>大眾服務企業集團公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>14,668</t>
+          <t>53,912</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,22 +1063,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>PEG US</t>
+          <t>GNRC US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>大眾服務企業集團公司</t>
+          <t>基內瑞克控股公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>53,912</t>
+          <t>14,668</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.14%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1100,24 +1100,24 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>14,609</t>
+          <t>35,127</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>35,127</t>
+          <t>14,609</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>VICR US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>懷克爾公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>11,485</t>
+          <t>54,026</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1195,22 +1195,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>VICR US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>懷克爾公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>54,026</t>
+          <t>11,485</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
@@ -1518,24 +1518,24 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.38%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>78,832</t>
+          <t>18,491</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>18,491</t>
+          <t>78,832</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>139,549,464</t>
+          <t>140,767,586</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
